--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A742DEA0-E274-48E1-A87E-7E52CE7ACD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F99E9C-42DA-4632-8D8B-447BDEF9A5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="24225" windowHeight="12660" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -182,7 +182,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -525,6 +546,7 @@
     <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -584,8 +606,8 @@
       <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
+      <c r="F2" s="5">
+        <v>1</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -603,15 +625,15 @@
         <v>14</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2" si="0">SUM(C2:K2)</f>
-        <v>2</v>
+        <f>SUM(C2:K2)</f>
+        <v>3</v>
       </c>
       <c r="M2">
         <f>SUM(B2:B11)</f>
         <v>0</v>
       </c>
       <c r="N2">
-        <f t="shared" ref="N2:N11" si="1">9-M2</f>
+        <f t="shared" ref="N2:N11" si="0">9-M2</f>
         <v>9</v>
       </c>
     </row>
@@ -647,19 +669,19 @@
       <c r="J3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>14</v>
+      <c r="K3" s="5">
+        <v>1</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L11" si="2">SUM(B3:K3)</f>
-        <v>1</v>
+        <f t="shared" ref="L3:L11" si="1">SUM(B3:K3)</f>
+        <v>2</v>
       </c>
       <c r="M3">
         <f>SUM(C2:C11)</f>
         <v>1</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -684,8 +706,8 @@
       <c r="F4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
+      <c r="G4" s="5">
+        <v>0</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>14</v>
@@ -700,16 +722,16 @@
         <v>14</v>
       </c>
       <c r="L4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -737,8 +759,8 @@
       <c r="G5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
+      <c r="H5" s="5">
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -750,16 +772,16 @@
         <v>14</v>
       </c>
       <c r="L5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M5">
         <f>SUM(E2:E11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -801,16 +823,16 @@
         <v>14</v>
       </c>
       <c r="L6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M6">
         <f>SUM(F2:F11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -827,7 +849,7 @@
       </c>
       <c r="D7" s="6">
         <f>IF(G4=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6">
         <f>IF(G5=0, 1, 0)</f>
@@ -853,15 +875,15 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
         <v>1</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -883,7 +905,7 @@
       </c>
       <c r="E8" s="6">
         <f>IF(H5=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6">
         <f>IF(H6=0, 1, 0)</f>
@@ -906,15 +928,15 @@
         <v>14</v>
       </c>
       <c r="L8">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
         <v>2</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -953,22 +975,22 @@
       <c r="I9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>14</v>
+      <c r="J9" s="5">
+        <v>1</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="L9">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="M9">
         <f>SUM(I2:I11)</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
@@ -1015,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M10">
         <f>SUM(J2:J11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1071,16 +1093,16 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M11">
         <f>SUM(K2:K11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1091,6 +1113,14 @@
       <pageSetup orientation="portrait" r:id="rId1"/>
     </customSheetView>
   </customSheetViews>
+  <conditionalFormatting sqref="N2:N11">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F99E9C-42DA-4632-8D8B-447BDEF9A5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2E07E-E9E1-4980-B377-4A91B70C3BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -182,7 +182,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -190,6 +190,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -539,17 +549,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13A2931-675D-49CA-B0C1-309266A4F919}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="11" width="15.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
@@ -590,7 +600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -637,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -648,8 +658,8 @@
       <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>14</v>
+      <c r="D3" s="5">
+        <v>0</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>14</v>
@@ -678,14 +688,14 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -695,7 +705,7 @@
       </c>
       <c r="C4" s="6">
         <f>IF(D3=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>10</v>
@@ -723,7 +733,7 @@
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
@@ -734,7 +744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -784,7 +794,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -819,8 +829,8 @@
       <c r="J6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>14</v>
+      <c r="K6" s="5">
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="1"/>
@@ -828,14 +838,14 @@
       </c>
       <c r="M6">
         <f>SUM(F2:F11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -887,7 +897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -921,8 +931,8 @@
       <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>14</v>
+      <c r="J8" s="5">
+        <v>0</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>14</v>
@@ -933,14 +943,14 @@
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -994,7 +1004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1024,7 +1034,7 @@
       </c>
       <c r="H10" s="6">
         <f>IF(J8=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="6">
         <f>IF(J9=0, 1, 0)</f>
@@ -1038,7 +1048,7 @@
       </c>
       <c r="L10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <f>SUM(J2:J11)</f>
@@ -1049,7 +1059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="F11" s="6">
         <f>IF(K6=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6">
         <f>IF(K7=0, 1, 0)</f>
@@ -1094,7 +1104,7 @@
       </c>
       <c r="L11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
         <f>SUM(K2:K11)</f>
@@ -1114,10 +1124,11 @@
     </customSheetView>
   </customSheetViews>
   <conditionalFormatting sqref="N2:N11">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="top10" dxfId="2" priority="1" bottom="1" rank="3"/>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2E07E-E9E1-4980-B377-4A91B70C3BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B619BE-4A70-41DE-9A11-6B01790D6D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -549,17 +549,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13A2931-675D-49CA-B0C1-309266A4F919}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="11" width="15.7265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1796875" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -613,8 +613,8 @@
       <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>14</v>
+      <c r="E2" s="5">
+        <v>1</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -636,7 +636,7 @@
       </c>
       <c r="L2">
         <f>SUM(C2:K2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <f>SUM(B2:B11)</f>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -695,7 +695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -744,7 +744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -787,14 +787,14 @@
       </c>
       <c r="M5">
         <f>SUM(E2:E11)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -845,7 +845,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -875,8 +875,8 @@
       <c r="H7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>14</v>
+      <c r="I7" s="5">
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>14</v>
@@ -890,14 +890,14 @@
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -950,7 +950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -976,7 +976,7 @@
       </c>
       <c r="G9" s="6">
         <f>IF(I7=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6">
         <f>IF(I8=0, 1, 0)</f>
@@ -993,7 +993,7 @@
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <f>SUM(I2:I11)</f>
@@ -1004,7 +1004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B619BE-4A70-41DE-9A11-6B01790D6D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDB84F2-FAC7-4821-8892-750398DC77A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -549,17 +549,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13A2931-675D-49CA-B0C1-309266A4F919}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7265625" customWidth="1"/>
+    <col min="2" max="11" width="15.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -695,7 +695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -713,8 +713,8 @@
       <c r="E4" s="5">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>14</v>
+      <c r="F4" s="5">
+        <v>1</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -733,7 +733,7 @@
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
@@ -744,7 +744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -775,8 +775,8 @@
       <c r="I5" s="5">
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>14</v>
+      <c r="J5" s="5">
+        <v>0</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>14</v>
@@ -787,14 +787,14 @@
       </c>
       <c r="M5">
         <f>SUM(E2:E11)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -838,14 +838,14 @@
       </c>
       <c r="M6">
         <f>SUM(F2:F11)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -872,8 +872,8 @@
       <c r="G7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
+      <c r="H7" s="5">
+        <v>0</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
@@ -890,14 +890,14 @@
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -923,7 +923,7 @@
       </c>
       <c r="G8" s="6">
         <f>IF(H7=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>10</v>
@@ -939,7 +939,7 @@
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
@@ -950,7 +950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E10" s="6">
         <f>IF(J5=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6">
         <f>IF(J6=0, 1, 0)</f>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="L10">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10">
         <f>SUM(J2:J11)</f>
@@ -1059,7 +1059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1124,7 +1124,7 @@
     </customSheetView>
   </customSheetViews>
   <conditionalFormatting sqref="N2:N11">
-    <cfRule type="top10" dxfId="2" priority="1" bottom="1" rank="3"/>
+    <cfRule type="top10" dxfId="2" priority="1" bottom="1" rank="4"/>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>4</formula>
     </cfRule>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDB84F2-FAC7-4821-8892-750398DC77A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCC2CF-F246-4750-BDCC-14B0CCE78EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="525" yWindow="3945" windowWidth="28800" windowHeight="15345" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -549,17 +549,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13A2931-675D-49CA-B0C1-309266A4F919}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" customWidth="1"/>
-    <col min="2" max="11" width="15.7265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1796875" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -628,15 +628,15 @@
       <c r="I2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>14</v>
+      <c r="J2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="5">
+        <v>1</v>
       </c>
       <c r="L2">
         <f>SUM(C2:K2)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
         <f>SUM(B2:B11)</f>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -670,11 +670,11 @@
       <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>14</v>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>14</v>
@@ -684,7 +684,7 @@
       </c>
       <c r="L3">
         <f t="shared" ref="L3:L11" si="1">SUM(B3:K3)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <f>SUM(C2:C11)</f>
@@ -695,7 +695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -728,12 +728,12 @@
       <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>14</v>
+      <c r="K4" s="5">
+        <v>1</v>
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
@@ -744,7 +744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -766,8 +766,8 @@
       <c r="F5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
+      <c r="G5" s="5">
+        <v>0</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -787,14 +787,14 @@
       </c>
       <c r="M5">
         <f>SUM(E2:E11)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -845,7 +845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -863,7 +863,7 @@
       </c>
       <c r="E7" s="6">
         <f>IF(G5=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6">
         <f>IF(G6=0, 1, 0)</f>
@@ -886,7 +886,7 @@
       </c>
       <c r="L7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
@@ -897,7 +897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -943,14 +943,14 @@
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -997,14 +997,14 @@
       </c>
       <c r="M9">
         <f>SUM(I2:I11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1052,14 +1052,14 @@
       </c>
       <c r="M10">
         <f>SUM(J2:J11)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1108,11 +1108,11 @@
       </c>
       <c r="M11">
         <f>SUM(K2:K11)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCC2CF-F246-4750-BDCC-14B0CCE78EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C1DBE1-D63E-4FE3-9861-D310DC6DE306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="3945" windowWidth="28800" windowHeight="15345" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -90,7 +90,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,8 +98,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +156,16 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -152,10 +176,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -178,31 +204,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -610,8 +620,8 @@
       <c r="C2" s="5">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>14</v>
+      <c r="D2" s="5">
+        <v>1</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
@@ -636,13 +646,13 @@
       </c>
       <c r="L2">
         <f>SUM(C2:K2)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <f>SUM(B2:B11)</f>
         <v>0</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="8">
         <f t="shared" ref="N2:N11" si="0">9-M2</f>
         <v>9</v>
       </c>
@@ -690,7 +700,7 @@
         <f>SUM(C2:C11)</f>
         <v>2</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -737,11 +747,11 @@
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
-        <v>1</v>
-      </c>
-      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="N4" s="9">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -820,11 +830,11 @@
       <c r="G6" s="5">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>14</v>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>14</v>
@@ -834,15 +844,15 @@
       </c>
       <c r="L6">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <f>SUM(F2:F11)</f>
+        <v>5</v>
+      </c>
+      <c r="N6" s="9">
+        <f t="shared" si="0"/>
         <v>4</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="0"/>
-        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -878,21 +888,21 @@
       <c r="I7" s="5">
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>14</v>
+      <c r="J7" s="5">
+        <v>1</v>
       </c>
       <c r="K7" s="5">
         <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
         <v>3</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -919,7 +929,7 @@
       </c>
       <c r="F8" s="6">
         <f>IF(H6=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6">
         <f>IF(H7=0, 1, 0)</f>
@@ -939,13 +949,13 @@
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
         <v>4</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -988,20 +998,20 @@
       <c r="J9" s="5">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>14</v>
+      <c r="K9" s="5">
+        <v>1</v>
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <f>SUM(I2:I11)</f>
-        <v>1</v>
-      </c>
-      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="N9" s="9">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1052,11 +1062,11 @@
       </c>
       <c r="M10">
         <f>SUM(J2:J11)</f>
+        <v>5</v>
+      </c>
+      <c r="N10" s="9">
+        <f t="shared" si="0"/>
         <v>4</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="0"/>
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1108,11 +1118,11 @@
       </c>
       <c r="M11">
         <f>SUM(K2:K11)</f>
+        <v>5</v>
+      </c>
+      <c r="N11" s="9">
+        <f t="shared" si="0"/>
         <v>4</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="0"/>
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1124,12 +1134,8 @@
     </customSheetView>
   </customSheetViews>
   <conditionalFormatting sqref="N2:N11">
-    <cfRule type="top10" dxfId="2" priority="1" bottom="1" rank="4"/>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
-      <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C1DBE1-D63E-4FE3-9861-D310DC6DE306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF51BFA-EC6F-4CB0-9300-6BCFB9514956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15285" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -671,8 +671,8 @@
       <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
+      <c r="E3" s="5">
+        <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="9">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -749,7 +749,7 @@
         <f>SUM(D2:D11)</f>
         <v>2</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -764,7 +764,7 @@
       </c>
       <c r="C5" s="6">
         <f>IF(E3=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="6">
         <f>IF(E4=0, 1, 0)</f>
@@ -793,7 +793,7 @@
       </c>
       <c r="L5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <f>SUM(E2:E11)</f>
@@ -1009,7 +1009,7 @@
         <f>SUM(I2:I11)</f>
         <v>2</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF51BFA-EC6F-4CB0-9300-6BCFB9514956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C577C41-CFFA-4339-9E28-B44BA4964C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15285" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -629,8 +629,8 @@
       <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
+      <c r="G2" s="5">
+        <v>1</v>
       </c>
       <c r="H2" s="5">
         <v>1</v>
@@ -646,7 +646,7 @@
       </c>
       <c r="L2">
         <f>SUM(C2:K2)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2">
         <f>SUM(B2:B11)</f>
@@ -686,21 +686,21 @@
       <c r="I3" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>14</v>
+      <c r="J3" s="5">
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" ref="L3:L11" si="1">SUM(B3:K3)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3">
         <f>SUM(C2:C11)</f>
         <v>3</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -732,8 +732,8 @@
       <c r="H4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>14</v>
+      <c r="I4" s="5">
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>1</v>
@@ -747,11 +747,11 @@
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" s="8">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -773,8 +773,8 @@
       <c r="E5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>14</v>
+      <c r="F5" s="5">
+        <v>1</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -793,7 +793,7 @@
       </c>
       <c r="L5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <f>SUM(E2:E11)</f>
@@ -848,11 +848,11 @@
       </c>
       <c r="M6">
         <f>SUM(F2:F11)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6" s="9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -900,11 +900,11 @@
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
-        <v>3</v>
-      </c>
-      <c r="N7" s="9">
+        <v>4</v>
+      </c>
+      <c r="N7" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -944,18 +944,18 @@
       <c r="J8" s="5">
         <v>0</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>14</v>
+      <c r="K8" s="5">
+        <v>1</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
         <v>4</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -974,7 +974,7 @@
       </c>
       <c r="D9" s="6">
         <f>IF(I4=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6">
         <f>IF(I5=0, 1, 0)</f>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <f>SUM(I2:I11)</f>
@@ -1062,11 +1062,11 @@
       </c>
       <c r="M10">
         <f>SUM(J2:J11)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10" s="9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1118,11 +1118,11 @@
       </c>
       <c r="M11">
         <f>SUM(K2:K11)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11" s="9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/PlayoffCalc.xlsx
+++ b/PlayoffCalc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A6123615\Documents\pyroject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C577C41-CFFA-4339-9E28-B44BA4964C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DD9E07-C713-400D-93B8-31CCF63DDB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25515" windowHeight="12975" xr2:uid="{D1863B8B-0EDB-480F-9AF9-012164597646}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
   <si>
     <t>ShiestyPeek</t>
   </si>
@@ -635,8 +635,8 @@
       <c r="H2" s="5">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
+      <c r="I2" s="5">
+        <v>0</v>
       </c>
       <c r="J2" s="5">
         <v>1</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="8">
         <f t="shared" ref="N2:N11" si="0">9-M2</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -677,8 +677,8 @@
       <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
+      <c r="G3" s="5">
+        <v>0</v>
       </c>
       <c r="H3" s="5">
         <v>1</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C11)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N3" s="8">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -729,8 +729,8 @@
       <c r="G4" s="5">
         <v>0</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>14</v>
+      <c r="H4" s="5">
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="L4">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <f>SUM(D2:D11)</f>
@@ -865,7 +865,7 @@
       </c>
       <c r="C7" s="6">
         <f>IF(G3=0, 1, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6">
         <f>IF(G4=0, 1, 0)</f>
@@ -896,7 +896,7 @@
       </c>
       <c r="L7">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <f>SUM(G2:G11)</f>
@@ -953,11 +953,11 @@
       </c>
       <c r="M8">
         <f>SUM(H2:H11)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N8" s="8">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -966,7 +966,7 @@
       </c>
       <c r="B9" s="6">
         <f>(IF(I2=0, 1, 0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="6">
         <f>IF(I3=0, 1, 0)</f>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="L9">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <f>SUM(I2:I11)</f>
